--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.01466230999911</v>
+        <v>7.152382625374855</v>
       </c>
       <c r="D2" t="n">
-        <v>39.89021594814325</v>
+        <v>6.482160091573278</v>
       </c>
       <c r="E2" t="n">
-        <v>17.1945387188285</v>
+        <v>2.794112541809631</v>
       </c>
       <c r="F2" t="n">
-        <v>12.88697047990422</v>
+        <v>2.094132702984435</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.0196078215513</v>
+        <v>8.453186271002087</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2770583391626</v>
+        <v>4.595021980113923</v>
       </c>
       <c r="E3" t="n">
-        <v>17.1945387188285</v>
+        <v>2.794112541809631</v>
       </c>
       <c r="F3" t="n">
-        <v>12.88697047990422</v>
+        <v>2.094132702984435</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.77576490409413</v>
+        <v>6.301061796915296</v>
       </c>
       <c r="D4" t="n">
-        <v>38.85969033220624</v>
+        <v>6.314699678983515</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1945387188285</v>
+        <v>2.794112541809631</v>
       </c>
       <c r="F4" t="n">
-        <v>12.88697047990422</v>
+        <v>2.094132702984435</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.750576352504869</v>
+        <v>1.096968657282041</v>
       </c>
       <c r="D5" t="n">
-        <v>7.827107452821352</v>
+        <v>1.27190496108347</v>
       </c>
       <c r="E5" t="n">
-        <v>17.1945387188285</v>
+        <v>2.794112541809631</v>
       </c>
       <c r="F5" t="n">
-        <v>12.88697047990422</v>
+        <v>2.094132702984435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
